--- a/reservation_forms/013_international_missions_form--reservation_forms.xlsx
+++ b/reservation_forms/013_international_missions_form--reservation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'category',_'label':_'category'}</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Category', 'label': 'Category'}</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -895,29 +895,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category',_'label':_'category'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category', 'label': 'Category'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category',_'label':_'category'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category', 'label': 'Category'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -929,97 +929,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'united_states',_'label':_'united_states'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'United States', 'label': 'United States'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>country_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'united_states',_'label':_'united_states'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'United States', 'label': 'United States'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>country_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'united_states',_'label':_'united_states'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'United States', 'label': 'United States'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_0,_'name':_'alabama',_'label':_'alabama'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 0, 'name': 'Alabama', 'label': 'Alabama'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'alabama',_'label':_'alabama'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Alabama', 'label': 'Alabama'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'alabama',_'label':_'alabama'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Alabama', 'label': 'Alabama'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
